--- a/行情复盘.xlsx
+++ b/行情复盘.xlsx
@@ -5,27 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\28565\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\my-project\stock-t-helper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D50AE0C-E2FF-4D62-BD59-CE62EE5E10CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E72912D8-07ED-46C6-A016-069899A5C38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="硕贝德" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -34,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="119">
   <si>
     <t>指标</t>
   </si>
@@ -350,6 +341,151 @@
   </si>
   <si>
     <t>说明该项需要每日动态修改，显示时需要标注红星号</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>市场</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>上升、下降转震荡、震荡、上升转震荡、下降</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>市场广度</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>涨停家数</t>
+  </si>
+  <si>
+    <t>跌停家数</t>
+  </si>
+  <si>
+    <t>大小盘对比</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>量能</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>昨日涨停表现</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>形态</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>情绪周期</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>15/10/7/9/2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>缩放量</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入 当日、近5日平局</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入 上涨家数、下跌家数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算公式：
+\[
+R=\left(\frac{V_{\text{today}}}{MA_5(V)}-1\right)\times100\%
+\]
+其中 \(V\) 为全市场成交额，\(MA_5(V)\) 为过去5个交易日的平均成交额。
+成交额变化率 基础分
+放量超过10% 10
+放量3%～10% 8
+变化在±3%以内 6
+缩量3%～10% 4
+缩量超过10% 2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算公式：
+\[
+B=\frac{N_{\text{涨}}-N_{\text{跌}}}
+{N_{\text{涨}}+N_{\text{跌}}}\times100\%
+\]
+其中 \(N_{\text{涨}}\) 和 \(N_{\text{跌}}\) 分别为上涨、下跌股票数量。平盘股票不纳入分母。
+广度指标 B 得分
+≥60% 15
+30%～60% 12
+10%～30% 9
+-10%～10% 6
+-30%～-10% 4
+-60%～-30% 2
+＜-60% 0</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择 大于100、80-100、65-80、50-65、少于50</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/8/6/0/-10</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择 少于8、8-15、15-25、多于25</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/2/-8/-16</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入 涨跌幅度</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>3*涨跌幅度</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>8/4/6/2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/8/6/2/-4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择 都强、大盘强、小盘强、都弱</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择 牛市、强势震荡、震荡、弱势震荡、熊市</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入 正数为放量、负数缩量</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择 启动、发酵、高潮、分歧、退潮、冰点</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6/10/6/2/-8/4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>公式：val/200 后四舍五入到小数点后一位</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>趋势</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -430,7 +566,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -468,11 +604,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF595959"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF595959"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF595959"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD8D8D8"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD8D8D8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD8D8D8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD8D8D8"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD8D8D8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD8D8D8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -515,6 +705,30 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -855,18 +1069,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G193"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:G203"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.625" customWidth="1"/>
-    <col min="2" max="2" width="99.25" customWidth="1"/>
-    <col min="3" max="3" width="30.25" customWidth="1"/>
-    <col min="4" max="4" width="58.25" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" customWidth="1"/>
+    <col min="2" max="2" width="99.21875" customWidth="1"/>
+    <col min="3" max="3" width="30.21875" customWidth="1"/>
+    <col min="4" max="4" width="58.21875" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
     <col min="6" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -885,7 +1099,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -904,7 +1118,7 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
     </row>
-    <row r="3" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>8</v>
       </c>
@@ -921,7 +1135,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
     </row>
-    <row r="4" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -938,7 +1152,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>11</v>
       </c>
@@ -955,7 +1169,7 @@
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
     </row>
-    <row r="6" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -972,7 +1186,7 @@
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
     </row>
-    <row r="7" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -989,7 +1203,7 @@
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
     </row>
-    <row r="8" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1006,7 +1220,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
     </row>
-    <row r="9" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>15</v>
       </c>
@@ -1023,7 +1237,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -1040,7 +1254,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
     </row>
-    <row r="11" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -1057,7 +1271,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
     </row>
-    <row r="12" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -1074,7 +1288,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
     </row>
-    <row r="13" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>19</v>
       </c>
@@ -1091,7 +1305,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
     </row>
-    <row r="14" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -1108,7 +1322,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
     </row>
-    <row r="15" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -1125,7 +1339,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
     </row>
-    <row r="16" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
@@ -1142,7 +1356,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
     </row>
-    <row r="17" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>25</v>
       </c>
@@ -1159,7 +1373,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
     </row>
-    <row r="18" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>26</v>
       </c>
@@ -1176,7 +1390,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
     </row>
-    <row r="19" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>27</v>
       </c>
@@ -1193,7 +1407,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
     </row>
-    <row r="20" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>71</v>
       </c>
@@ -1210,7 +1424,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
     </row>
-    <row r="21" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>72</v>
       </c>
@@ -1227,7 +1441,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
     </row>
-    <row r="22" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
@@ -1244,7 +1458,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
     </row>
-    <row r="23" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
@@ -1261,7 +1475,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
     </row>
-    <row r="24" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>31</v>
       </c>
@@ -1278,139 +1492,203 @@
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
     </row>
-    <row r="25" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="15" t="s">
         <v>80</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
     </row>
-    <row r="26" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
+    <row r="26" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" s="22"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
     </row>
-    <row r="27" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
+    <row r="27" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E27" s="22"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
     </row>
-    <row r="28" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
+    <row r="28" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" s="22"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
     </row>
-    <row r="29" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
+    <row r="29" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="22"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
     </row>
-    <row r="30" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
+    <row r="30" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="E30" s="22"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
     </row>
-    <row r="31" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
+    <row r="31" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" s="22"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
     </row>
-    <row r="32" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
+    <row r="32" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" s="22"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
     </row>
-    <row r="33" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
+    <row r="33" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33" s="22"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
     </row>
-    <row r="34" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
+    <row r="34" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E34" s="22"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
     </row>
-    <row r="35" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
+    <row r="35" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E35" s="22"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
     </row>
-    <row r="36" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
+    <row r="36" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
     </row>
-    <row r="37" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1419,43 +1697,59 @@
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
     </row>
-    <row r="38" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
+    <row r="38" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
     </row>
-    <row r="39" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
+    <row r="39" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>84</v>
+      </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
     </row>
-    <row r="40" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
+    <row r="40" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>85</v>
+      </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
     </row>
-    <row r="41" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
+    <row r="41" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>87</v>
+      </c>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
     </row>
-    <row r="42" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -1464,7 +1758,7 @@
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
     </row>
-    <row r="43" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -1473,7 +1767,7 @@
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
     </row>
-    <row r="44" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -1482,7 +1776,7 @@
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
     </row>
-    <row r="45" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -1491,7 +1785,7 @@
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
     </row>
-    <row r="46" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -1500,7 +1794,7 @@
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
     </row>
-    <row r="47" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -1509,7 +1803,7 @@
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
     </row>
-    <row r="48" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -1518,7 +1812,7 @@
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
     </row>
-    <row r="49" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -1527,7 +1821,7 @@
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
     </row>
-    <row r="50" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -1536,7 +1830,7 @@
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
     </row>
-    <row r="51" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -1545,7 +1839,7 @@
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
     </row>
-    <row r="52" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -1554,7 +1848,7 @@
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
     </row>
-    <row r="53" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -1563,7 +1857,7 @@
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
     </row>
-    <row r="54" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -1572,7 +1866,7 @@
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
     </row>
-    <row r="55" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -1581,7 +1875,7 @@
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
     </row>
-    <row r="56" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -1590,7 +1884,7 @@
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
     </row>
-    <row r="57" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -1599,7 +1893,7 @@
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
     </row>
-    <row r="58" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -1608,7 +1902,7 @@
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
     </row>
-    <row r="59" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -1617,7 +1911,7 @@
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
     </row>
-    <row r="60" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -1626,7 +1920,7 @@
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
     </row>
-    <row r="61" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -1635,7 +1929,7 @@
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
     </row>
-    <row r="62" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -1644,7 +1938,7 @@
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
     </row>
-    <row r="63" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -1653,7 +1947,7 @@
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
     </row>
-    <row r="64" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -1662,7 +1956,7 @@
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
     </row>
-    <row r="65" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -1671,7 +1965,7 @@
       <c r="F65" s="6"/>
       <c r="G65" s="6"/>
     </row>
-    <row r="66" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -1680,7 +1974,7 @@
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
     </row>
-    <row r="67" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -1689,7 +1983,7 @@
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
     </row>
-    <row r="68" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -1698,7 +1992,7 @@
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
     </row>
-    <row r="69" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -1707,7 +2001,7 @@
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
     </row>
-    <row r="70" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -1716,7 +2010,7 @@
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
     </row>
-    <row r="71" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -1725,7 +2019,7 @@
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
     </row>
-    <row r="72" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -1734,7 +2028,7 @@
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
     </row>
-    <row r="73" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -1743,7 +2037,7 @@
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
     </row>
-    <row r="74" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -1752,7 +2046,7 @@
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
     </row>
-    <row r="75" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -1761,7 +2055,7 @@
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
     </row>
-    <row r="76" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -1770,7 +2064,7 @@
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
     </row>
-    <row r="77" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -1779,7 +2073,7 @@
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
     </row>
-    <row r="78" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -1788,7 +2082,7 @@
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
     </row>
-    <row r="79" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -1797,7 +2091,7 @@
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
     </row>
-    <row r="80" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -1806,7 +2100,7 @@
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
     </row>
-    <row r="81" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -1815,7 +2109,7 @@
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
     </row>
-    <row r="82" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -1824,7 +2118,7 @@
       <c r="F82" s="6"/>
       <c r="G82" s="6"/>
     </row>
-    <row r="83" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -1833,7 +2127,7 @@
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
     </row>
-    <row r="84" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -1842,7 +2136,7 @@
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
     </row>
-    <row r="85" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -1851,7 +2145,7 @@
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
     </row>
-    <row r="86" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -1860,7 +2154,7 @@
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
     </row>
-    <row r="87" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -1869,7 +2163,7 @@
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
     </row>
-    <row r="88" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -1878,7 +2172,7 @@
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
     </row>
-    <row r="89" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -1887,7 +2181,7 @@
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
     </row>
-    <row r="90" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -1896,7 +2190,7 @@
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
     </row>
-    <row r="91" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -1905,7 +2199,7 @@
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
     </row>
-    <row r="92" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -1914,7 +2208,7 @@
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
     </row>
-    <row r="93" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -1923,7 +2217,7 @@
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
     </row>
-    <row r="94" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -1932,7 +2226,7 @@
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
     </row>
-    <row r="95" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -1941,7 +2235,7 @@
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
     </row>
-    <row r="96" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -1950,7 +2244,7 @@
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
     </row>
-    <row r="97" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -1959,7 +2253,7 @@
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
     </row>
-    <row r="98" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -1968,7 +2262,7 @@
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
     </row>
-    <row r="99" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -1977,7 +2271,7 @@
       <c r="F99" s="6"/>
       <c r="G99" s="6"/>
     </row>
-    <row r="100" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -1986,7 +2280,7 @@
       <c r="F100" s="6"/>
       <c r="G100" s="6"/>
     </row>
-    <row r="101" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -1995,7 +2289,7 @@
       <c r="F101" s="6"/>
       <c r="G101" s="6"/>
     </row>
-    <row r="102" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -2004,7 +2298,7 @@
       <c r="F102" s="6"/>
       <c r="G102" s="6"/>
     </row>
-    <row r="103" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -2013,7 +2307,7 @@
       <c r="F103" s="6"/>
       <c r="G103" s="6"/>
     </row>
-    <row r="104" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -2022,7 +2316,7 @@
       <c r="F104" s="6"/>
       <c r="G104" s="6"/>
     </row>
-    <row r="105" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
@@ -2031,7 +2325,7 @@
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
     </row>
-    <row r="106" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -2040,7 +2334,7 @@
       <c r="F106" s="6"/>
       <c r="G106" s="6"/>
     </row>
-    <row r="107" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
@@ -2049,7 +2343,7 @@
       <c r="F107" s="6"/>
       <c r="G107" s="6"/>
     </row>
-    <row r="108" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
@@ -2058,7 +2352,7 @@
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
     </row>
-    <row r="109" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -2067,7 +2361,7 @@
       <c r="F109" s="6"/>
       <c r="G109" s="6"/>
     </row>
-    <row r="110" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
@@ -2076,7 +2370,7 @@
       <c r="F110" s="6"/>
       <c r="G110" s="6"/>
     </row>
-    <row r="111" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6"/>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
@@ -2085,7 +2379,7 @@
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
     </row>
-    <row r="112" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
@@ -2094,7 +2388,7 @@
       <c r="F112" s="6"/>
       <c r="G112" s="6"/>
     </row>
-    <row r="113" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
@@ -2103,7 +2397,7 @@
       <c r="F113" s="6"/>
       <c r="G113" s="6"/>
     </row>
-    <row r="114" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6"/>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
@@ -2112,7 +2406,7 @@
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
     </row>
-    <row r="115" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
@@ -2121,7 +2415,7 @@
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
     </row>
-    <row r="116" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6"/>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
@@ -2130,7 +2424,7 @@
       <c r="F116" s="6"/>
       <c r="G116" s="6"/>
     </row>
-    <row r="117" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6"/>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
@@ -2139,7 +2433,7 @@
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
     </row>
-    <row r="118" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
@@ -2148,7 +2442,7 @@
       <c r="F118" s="6"/>
       <c r="G118" s="6"/>
     </row>
-    <row r="119" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="6"/>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
@@ -2157,7 +2451,7 @@
       <c r="F119" s="6"/>
       <c r="G119" s="6"/>
     </row>
-    <row r="120" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
@@ -2166,7 +2460,7 @@
       <c r="F120" s="6"/>
       <c r="G120" s="6"/>
     </row>
-    <row r="121" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
@@ -2175,7 +2469,7 @@
       <c r="F121" s="6"/>
       <c r="G121" s="6"/>
     </row>
-    <row r="122" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
@@ -2184,7 +2478,7 @@
       <c r="F122" s="6"/>
       <c r="G122" s="6"/>
     </row>
-    <row r="123" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6"/>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
@@ -2193,7 +2487,7 @@
       <c r="F123" s="6"/>
       <c r="G123" s="6"/>
     </row>
-    <row r="124" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6"/>
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
@@ -2202,7 +2496,7 @@
       <c r="F124" s="6"/>
       <c r="G124" s="6"/>
     </row>
-    <row r="125" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6"/>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
@@ -2211,7 +2505,7 @@
       <c r="F125" s="6"/>
       <c r="G125" s="6"/>
     </row>
-    <row r="126" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6"/>
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
@@ -2220,7 +2514,7 @@
       <c r="F126" s="6"/>
       <c r="G126" s="6"/>
     </row>
-    <row r="127" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="6"/>
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
@@ -2229,7 +2523,7 @@
       <c r="F127" s="6"/>
       <c r="G127" s="6"/>
     </row>
-    <row r="128" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
@@ -2238,7 +2532,7 @@
       <c r="F128" s="6"/>
       <c r="G128" s="6"/>
     </row>
-    <row r="129" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="6"/>
       <c r="B129" s="6"/>
       <c r="C129" s="6"/>
@@ -2247,7 +2541,7 @@
       <c r="F129" s="6"/>
       <c r="G129" s="6"/>
     </row>
-    <row r="130" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6"/>
       <c r="B130" s="6"/>
       <c r="C130" s="6"/>
@@ -2256,7 +2550,7 @@
       <c r="F130" s="6"/>
       <c r="G130" s="6"/>
     </row>
-    <row r="131" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="6"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
@@ -2265,7 +2559,7 @@
       <c r="F131" s="6"/>
       <c r="G131" s="6"/>
     </row>
-    <row r="132" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6"/>
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
@@ -2274,7 +2568,7 @@
       <c r="F132" s="6"/>
       <c r="G132" s="6"/>
     </row>
-    <row r="133" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6"/>
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
@@ -2283,7 +2577,7 @@
       <c r="F133" s="6"/>
       <c r="G133" s="6"/>
     </row>
-    <row r="134" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6"/>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
@@ -2292,7 +2586,7 @@
       <c r="F134" s="6"/>
       <c r="G134" s="6"/>
     </row>
-    <row r="135" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="6"/>
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
@@ -2301,7 +2595,7 @@
       <c r="F135" s="6"/>
       <c r="G135" s="6"/>
     </row>
-    <row r="136" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
@@ -2310,7 +2604,7 @@
       <c r="F136" s="6"/>
       <c r="G136" s="6"/>
     </row>
-    <row r="137" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="6"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
@@ -2319,7 +2613,7 @@
       <c r="F137" s="6"/>
       <c r="G137" s="6"/>
     </row>
-    <row r="138" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6"/>
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
@@ -2328,7 +2622,7 @@
       <c r="F138" s="6"/>
       <c r="G138" s="6"/>
     </row>
-    <row r="139" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="6"/>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
@@ -2337,7 +2631,7 @@
       <c r="F139" s="6"/>
       <c r="G139" s="6"/>
     </row>
-    <row r="140" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
@@ -2346,7 +2640,7 @@
       <c r="F140" s="6"/>
       <c r="G140" s="6"/>
     </row>
-    <row r="141" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="6"/>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
@@ -2355,7 +2649,7 @@
       <c r="F141" s="6"/>
       <c r="G141" s="6"/>
     </row>
-    <row r="142" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6"/>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
@@ -2364,7 +2658,7 @@
       <c r="F142" s="6"/>
       <c r="G142" s="6"/>
     </row>
-    <row r="143" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="6"/>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
@@ -2373,7 +2667,7 @@
       <c r="F143" s="6"/>
       <c r="G143" s="6"/>
     </row>
-    <row r="144" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6"/>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
@@ -2382,7 +2676,7 @@
       <c r="F144" s="6"/>
       <c r="G144" s="6"/>
     </row>
-    <row r="145" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="6"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
@@ -2391,7 +2685,7 @@
       <c r="F145" s="6"/>
       <c r="G145" s="6"/>
     </row>
-    <row r="146" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6"/>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
@@ -2400,7 +2694,7 @@
       <c r="F146" s="6"/>
       <c r="G146" s="6"/>
     </row>
-    <row r="147" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="6"/>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
@@ -2409,7 +2703,7 @@
       <c r="F147" s="6"/>
       <c r="G147" s="6"/>
     </row>
-    <row r="148" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6"/>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
@@ -2418,7 +2712,7 @@
       <c r="F148" s="6"/>
       <c r="G148" s="6"/>
     </row>
-    <row r="149" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="6"/>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
@@ -2427,7 +2721,7 @@
       <c r="F149" s="6"/>
       <c r="G149" s="6"/>
     </row>
-    <row r="150" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6"/>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
@@ -2436,7 +2730,7 @@
       <c r="F150" s="6"/>
       <c r="G150" s="6"/>
     </row>
-    <row r="151" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="6"/>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
@@ -2445,7 +2739,7 @@
       <c r="F151" s="6"/>
       <c r="G151" s="6"/>
     </row>
-    <row r="152" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6"/>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
@@ -2454,7 +2748,7 @@
       <c r="F152" s="6"/>
       <c r="G152" s="6"/>
     </row>
-    <row r="153" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="6"/>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
@@ -2463,7 +2757,7 @@
       <c r="F153" s="6"/>
       <c r="G153" s="6"/>
     </row>
-    <row r="154" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
@@ -2472,7 +2766,7 @@
       <c r="F154" s="6"/>
       <c r="G154" s="6"/>
     </row>
-    <row r="155" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="6"/>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
@@ -2481,7 +2775,7 @@
       <c r="F155" s="6"/>
       <c r="G155" s="6"/>
     </row>
-    <row r="156" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6"/>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
@@ -2490,7 +2784,7 @@
       <c r="F156" s="6"/>
       <c r="G156" s="6"/>
     </row>
-    <row r="157" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="6"/>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
@@ -2499,7 +2793,7 @@
       <c r="F157" s="6"/>
       <c r="G157" s="6"/>
     </row>
-    <row r="158" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6"/>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
@@ -2508,7 +2802,7 @@
       <c r="F158" s="6"/>
       <c r="G158" s="6"/>
     </row>
-    <row r="159" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="6"/>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
@@ -2517,7 +2811,7 @@
       <c r="F159" s="6"/>
       <c r="G159" s="6"/>
     </row>
-    <row r="160" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6"/>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
@@ -2526,7 +2820,7 @@
       <c r="F160" s="6"/>
       <c r="G160" s="6"/>
     </row>
-    <row r="161" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="6"/>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
@@ -2535,7 +2829,7 @@
       <c r="F161" s="6"/>
       <c r="G161" s="6"/>
     </row>
-    <row r="162" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="6"/>
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
@@ -2544,7 +2838,7 @@
       <c r="F162" s="6"/>
       <c r="G162" s="6"/>
     </row>
-    <row r="163" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="6"/>
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
@@ -2553,7 +2847,7 @@
       <c r="F163" s="6"/>
       <c r="G163" s="6"/>
     </row>
-    <row r="164" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="6"/>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
@@ -2562,7 +2856,7 @@
       <c r="F164" s="6"/>
       <c r="G164" s="6"/>
     </row>
-    <row r="165" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="6"/>
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
@@ -2571,7 +2865,7 @@
       <c r="F165" s="6"/>
       <c r="G165" s="6"/>
     </row>
-    <row r="166" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="6"/>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
@@ -2580,7 +2874,7 @@
       <c r="F166" s="6"/>
       <c r="G166" s="6"/>
     </row>
-    <row r="167" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="6"/>
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
@@ -2589,7 +2883,7 @@
       <c r="F167" s="6"/>
       <c r="G167" s="6"/>
     </row>
-    <row r="168" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6"/>
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
@@ -2598,7 +2892,7 @@
       <c r="F168" s="6"/>
       <c r="G168" s="6"/>
     </row>
-    <row r="169" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="6"/>
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
@@ -2607,7 +2901,7 @@
       <c r="F169" s="6"/>
       <c r="G169" s="6"/>
     </row>
-    <row r="170" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="6"/>
       <c r="B170" s="6"/>
       <c r="C170" s="6"/>
@@ -2616,7 +2910,7 @@
       <c r="F170" s="6"/>
       <c r="G170" s="6"/>
     </row>
-    <row r="171" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="6"/>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
@@ -2625,7 +2919,7 @@
       <c r="F171" s="6"/>
       <c r="G171" s="6"/>
     </row>
-    <row r="172" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="6"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
@@ -2634,7 +2928,7 @@
       <c r="F172" s="6"/>
       <c r="G172" s="6"/>
     </row>
-    <row r="173" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="6"/>
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
@@ -2643,7 +2937,7 @@
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
     </row>
-    <row r="174" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="6"/>
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
@@ -2652,7 +2946,7 @@
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
     </row>
-    <row r="175" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="6"/>
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
@@ -2661,7 +2955,7 @@
       <c r="F175" s="6"/>
       <c r="G175" s="6"/>
     </row>
-    <row r="176" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="6"/>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
@@ -2670,7 +2964,7 @@
       <c r="F176" s="6"/>
       <c r="G176" s="6"/>
     </row>
-    <row r="177" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="6"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
@@ -2679,7 +2973,7 @@
       <c r="F177" s="6"/>
       <c r="G177" s="6"/>
     </row>
-    <row r="178" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="6"/>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
@@ -2688,7 +2982,7 @@
       <c r="F178" s="6"/>
       <c r="G178" s="6"/>
     </row>
-    <row r="179" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="6"/>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
@@ -2697,7 +2991,7 @@
       <c r="F179" s="6"/>
       <c r="G179" s="6"/>
     </row>
-    <row r="180" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="6"/>
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
@@ -2706,7 +3000,7 @@
       <c r="F180" s="6"/>
       <c r="G180" s="6"/>
     </row>
-    <row r="181" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
@@ -2715,7 +3009,7 @@
       <c r="F181" s="6"/>
       <c r="G181" s="6"/>
     </row>
-    <row r="182" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="6"/>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
@@ -2724,7 +3018,7 @@
       <c r="F182" s="6"/>
       <c r="G182" s="6"/>
     </row>
-    <row r="183" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="6"/>
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
@@ -2733,7 +3027,7 @@
       <c r="F183" s="6"/>
       <c r="G183" s="6"/>
     </row>
-    <row r="184" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="6"/>
       <c r="B184" s="6"/>
       <c r="C184" s="6"/>
@@ -2742,7 +3036,7 @@
       <c r="F184" s="6"/>
       <c r="G184" s="6"/>
     </row>
-    <row r="185" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
@@ -2751,7 +3045,7 @@
       <c r="F185" s="6"/>
       <c r="G185" s="6"/>
     </row>
-    <row r="186" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="6"/>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
@@ -2760,7 +3054,7 @@
       <c r="F186" s="6"/>
       <c r="G186" s="6"/>
     </row>
-    <row r="187" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="6"/>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
@@ -2769,7 +3063,7 @@
       <c r="F187" s="6"/>
       <c r="G187" s="6"/>
     </row>
-    <row r="188" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="6"/>
       <c r="B188" s="6"/>
       <c r="C188" s="6"/>
@@ -2778,7 +3072,7 @@
       <c r="F188" s="6"/>
       <c r="G188" s="6"/>
     </row>
-    <row r="189" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="6"/>
       <c r="B189" s="6"/>
       <c r="C189" s="6"/>
@@ -2787,7 +3081,7 @@
       <c r="F189" s="6"/>
       <c r="G189" s="6"/>
     </row>
-    <row r="190" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="6"/>
       <c r="B190" s="6"/>
       <c r="C190" s="6"/>
@@ -2796,7 +3090,7 @@
       <c r="F190" s="6"/>
       <c r="G190" s="6"/>
     </row>
-    <row r="191" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="6"/>
       <c r="B191" s="6"/>
       <c r="C191" s="6"/>
@@ -2805,7 +3099,7 @@
       <c r="F191" s="6"/>
       <c r="G191" s="6"/>
     </row>
-    <row r="192" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="6"/>
       <c r="B192" s="6"/>
       <c r="C192" s="6"/>
@@ -2814,7 +3108,7 @@
       <c r="F192" s="6"/>
       <c r="G192" s="6"/>
     </row>
-    <row r="193" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="6"/>
       <c r="B193" s="6"/>
       <c r="C193" s="6"/>
@@ -2823,6 +3117,96 @@
       <c r="F193" s="6"/>
       <c r="G193" s="6"/>
     </row>
+    <row r="194" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="6"/>
+      <c r="B194" s="6"/>
+      <c r="C194" s="6"/>
+      <c r="D194" s="6"/>
+      <c r="E194" s="6"/>
+      <c r="F194" s="6"/>
+      <c r="G194" s="6"/>
+    </row>
+    <row r="195" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="6"/>
+      <c r="B195" s="6"/>
+      <c r="C195" s="6"/>
+      <c r="D195" s="6"/>
+      <c r="E195" s="6"/>
+      <c r="F195" s="6"/>
+      <c r="G195" s="6"/>
+    </row>
+    <row r="196" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="6"/>
+      <c r="B196" s="6"/>
+      <c r="C196" s="6"/>
+      <c r="D196" s="6"/>
+      <c r="E196" s="6"/>
+      <c r="F196" s="6"/>
+      <c r="G196" s="6"/>
+    </row>
+    <row r="197" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="6"/>
+      <c r="B197" s="6"/>
+      <c r="C197" s="6"/>
+      <c r="D197" s="6"/>
+      <c r="E197" s="6"/>
+      <c r="F197" s="6"/>
+      <c r="G197" s="6"/>
+    </row>
+    <row r="198" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="6"/>
+      <c r="B198" s="6"/>
+      <c r="C198" s="6"/>
+      <c r="D198" s="6"/>
+      <c r="E198" s="6"/>
+      <c r="F198" s="6"/>
+      <c r="G198" s="6"/>
+    </row>
+    <row r="199" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="6"/>
+      <c r="B199" s="6"/>
+      <c r="C199" s="6"/>
+      <c r="D199" s="6"/>
+      <c r="E199" s="6"/>
+      <c r="F199" s="6"/>
+      <c r="G199" s="6"/>
+    </row>
+    <row r="200" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="6"/>
+      <c r="B200" s="6"/>
+      <c r="C200" s="6"/>
+      <c r="D200" s="6"/>
+      <c r="E200" s="6"/>
+      <c r="F200" s="6"/>
+      <c r="G200" s="6"/>
+    </row>
+    <row r="201" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="6"/>
+      <c r="B201" s="6"/>
+      <c r="C201" s="6"/>
+      <c r="D201" s="6"/>
+      <c r="E201" s="6"/>
+      <c r="F201" s="6"/>
+      <c r="G201" s="6"/>
+    </row>
+    <row r="202" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="6"/>
+      <c r="B202" s="6"/>
+      <c r="C202" s="6"/>
+      <c r="D202" s="6"/>
+      <c r="E202" s="6"/>
+      <c r="F202" s="6"/>
+      <c r="G202" s="6"/>
+    </row>
+    <row r="203" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="6"/>
+      <c r="B203" s="6"/>
+      <c r="C203" s="6"/>
+      <c r="D203" s="6"/>
+      <c r="E203" s="6"/>
+      <c r="F203" s="6"/>
+      <c r="G203" s="6"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
